--- a/artfynd/A 50336-2020 artfynd.xlsx
+++ b/artfynd/A 50336-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50336-2020 artfynd.xlsx
+++ b/artfynd/A 50336-2020 artfynd.xlsx
@@ -922,12 +922,7 @@
         <v>124235407</v>
       </c>
       <c r="B4" t="n">
-        <v>57534</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57653</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50336-2020 artfynd.xlsx
+++ b/artfynd/A 50336-2020 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>124235407</v>
       </c>
       <c r="B4" t="n">
-        <v>57653</v>
+        <v>57655</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50336-2020 artfynd.xlsx
+++ b/artfynd/A 50336-2020 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>124235407</v>
       </c>
       <c r="B4" t="n">
-        <v>57655</v>
+        <v>57658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50336-2020 artfynd.xlsx
+++ b/artfynd/A 50336-2020 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>124235407</v>
       </c>
       <c r="B4" t="n">
-        <v>57658</v>
+        <v>57664</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50336-2020 artfynd.xlsx
+++ b/artfynd/A 50336-2020 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>124235407</v>
       </c>
       <c r="B4" t="n">
-        <v>57664</v>
+        <v>57665</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50336-2020 artfynd.xlsx
+++ b/artfynd/A 50336-2020 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>124235407</v>
       </c>
       <c r="B4" t="n">
-        <v>57665</v>
+        <v>57676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
